--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,442 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128326375</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106315</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>727894</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6369083</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>dubbelsidigISDennis Nyström</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128322860</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>727894</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6369082</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>dubbelsidigISDennis Nyström</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128324424</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Salepsrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anacamptis pyramidalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>727883</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6369093</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>norraISMarie Björklund</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128326812</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110581</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>727887</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6369090</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>norraISMarie Björklund</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>106315</v>
+        <v>103935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,23 +800,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -831,7 +827,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>103930</v>
+        <v>106320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,19 +906,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98360</v>
+        <v>98365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110581</v>
+        <v>110586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B3" t="n">
-        <v>103935</v>
+        <v>106413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,19 +800,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -827,7 +831,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B4" t="n">
-        <v>106320</v>
+        <v>104028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,23 +910,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110586</v>
+        <v>110679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>106413</v>
+        <v>104049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,23 +800,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -831,7 +827,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>104028</v>
+        <v>106435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,19 +906,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98458</v>
+        <v>98472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110679</v>
+        <v>110705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B3" t="n">
-        <v>104049</v>
+        <v>106447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,19 +800,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -827,7 +831,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B4" t="n">
-        <v>106435</v>
+        <v>104061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,23 +910,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98472</v>
+        <v>98475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110705</v>
+        <v>110718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128326375</v>
       </c>
       <c r="B3" t="n">
-        <v>106447</v>
+        <v>106456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128322860</v>
       </c>
       <c r="B4" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98475</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110718</v>
+        <v>110727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>106456</v>
+        <v>104073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,23 +800,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -831,7 +827,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>104070</v>
+        <v>106461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,19 +906,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110727</v>
+        <v>110732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>106489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98479</v>
+        <v>98506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110732</v>
+        <v>110760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>106489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,19 +800,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -827,7 +831,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B4" t="n">
-        <v>106489</v>
+        <v>104100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,23 +910,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>106489</v>
+        <v>104113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,23 +800,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -831,7 +827,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>104100</v>
+        <v>106502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,19 +906,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98506</v>
+        <v>98519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110760</v>
+        <v>110773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B3" t="n">
-        <v>104113</v>
+        <v>106502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,19 +800,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -827,7 +831,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B4" t="n">
-        <v>106502</v>
+        <v>104113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,23 +910,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128326375</v>
+        <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>106502</v>
+        <v>104113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,23 +800,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -831,7 +827,7 @@
         <v>727894</v>
       </c>
       <c r="R3" t="n">
-        <v>6369083</v>
+        <v>6369082</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128322860</v>
+        <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>104113</v>
+        <v>106502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,19 +906,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -937,7 +937,7 @@
         <v>727894</v>
       </c>
       <c r="R4" t="n">
-        <v>6369082</v>
+        <v>6369083</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128322860</v>
       </c>
       <c r="B3" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128326375</v>
       </c>
       <c r="B4" t="n">
-        <v>106502</v>
+        <v>106506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128324424</v>
       </c>
       <c r="B5" t="n">
-        <v>98519</v>
+        <v>98523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128326812</v>
       </c>
       <c r="B6" t="n">
-        <v>110773</v>
+        <v>110777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112823177</v>
+        <v>128324424</v>
       </c>
       <c r="B2" t="n">
-        <v>56694</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102622</v>
+        <v>49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Salepsrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Anacamptis pyramidalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kyrkljuves, Gammelgarn k:a, Gtl</t>
+          <t>Artrik vägkant, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728001</v>
+        <v>727883</v>
       </c>
       <c r="R2" t="n">
-        <v>6369062</v>
+        <v>6369093</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>norraISMarie Björklund</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +769,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Andersson</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Nilsson, Sebbe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128322860</v>
+        <v>1912379</v>
       </c>
       <c r="B3" t="n">
-        <v>104117</v>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>(06J3f16), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727894</v>
+        <v>727961</v>
       </c>
       <c r="R3" t="n">
-        <v>6369082</v>
+        <v>6369369</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,17 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>1998-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>1998-06-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>dubbelsidigISDennis Nyström</t>
+          <t>060935161 / ART LEUC / Enstaka-sparsam (1)  / OBJ.AREA:3 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,48 +875,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Magnus Stenmark</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326375</v>
+        <v>26828646</v>
       </c>
       <c r="B4" t="n">
-        <v>106506</v>
+        <v>57754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -928,19 +924,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>Kyrkljuves, Gammelgarn k:a, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727894</v>
+        <v>728001</v>
       </c>
       <c r="R4" t="n">
-        <v>6369083</v>
+        <v>6369062</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,17 +965,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2007-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2007-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>23:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>dubbelsidigISDennis Nyström</t>
+          <t>Spelande ca 200m SV om.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,68 +1000,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Björn Lilja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Magnus Stenmark</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Björn Lilja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128324424</v>
+        <v>23708890</v>
       </c>
       <c r="B5" t="n">
-        <v>98523</v>
+        <v>57942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>102119</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salepsrot</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anacamptis pyramidalis</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>Kyrkljuves, Gammelgarn k:a, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727883</v>
+        <v>728001</v>
       </c>
       <c r="R5" t="n">
-        <v>6369093</v>
+        <v>6369062</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,17 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2006-05-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>norraISMarie Björklund</t>
+          <t>2006-05-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,48 +1116,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Jim Sundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Magnus Stenmark</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128326812</v>
+        <v>76864855</v>
       </c>
       <c r="B6" t="n">
-        <v>110777</v>
+        <v>57785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219719</v>
+        <v>102622</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Säfferot</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Seseli libanotis</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. D. J. Koch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,19 +1161,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>Kyrkljuves, Gammelgarn k:a, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727887</v>
+        <v>728001</v>
       </c>
       <c r="R6" t="n">
-        <v>6369090</v>
+        <v>6369062</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,17 +1205,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2019-04-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2019-04-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>norraISMarie Björklund</t>
+          <t>Öster om Nobells lammgård</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,17 +1240,566 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Sebbe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebbe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23452109</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kyrkljuves, Gammelgarn k:a, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>728001</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6369062</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2006-05-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2006-05-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128326812</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>727887</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6369090</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>norraISMarie Björklund</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Via Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128326375</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>727894</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6369083</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>dubbelsidigISDennis Nyström</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128322860</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>727894</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6369082</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>dubbelsidigISDennis Nyström</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6525464</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>(06J3f16), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>727961</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6369369</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1998-06-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1998-06-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>060935161 / THE LEPA / Enstaka-sparsam (1)  / OBJ.AREA:3 ha</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 66091-2021 artfynd.xlsx
+++ b/artfynd/A 66091-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128324424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1912379</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26828646</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23708890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76864855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23452109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128326812</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128326375</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128322860</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,8 +1852,25 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6525464</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>